--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.76682033401551</v>
+        <v>5.16210830427752</v>
       </c>
       <c r="D2" t="n">
-        <v>6.506471515385998</v>
+        <v>1.057301621250225</v>
       </c>
       <c r="E2" t="n">
-        <v>7.725566464509935</v>
+        <v>1.255404550482864</v>
       </c>
       <c r="F2" t="n">
-        <v>16.36849919180995</v>
+        <v>2.659881118669115</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.8164862416155</v>
+        <v>3.707679014262518</v>
       </c>
       <c r="D3" t="n">
-        <v>5.407030387879013</v>
+        <v>0.8786424380303397</v>
       </c>
       <c r="E3" t="n">
-        <v>7.725566464509935</v>
+        <v>1.255404550482864</v>
       </c>
       <c r="F3" t="n">
-        <v>16.36849919180995</v>
+        <v>2.659881118669115</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.11587175855455</v>
+        <v>4.568829160765115</v>
       </c>
       <c r="D4" t="n">
-        <v>8.969576237308265</v>
+        <v>1.457556138562593</v>
       </c>
       <c r="E4" t="n">
-        <v>7.725566464509935</v>
+        <v>1.255404550482864</v>
       </c>
       <c r="F4" t="n">
-        <v>16.36849919180995</v>
+        <v>2.659881118669115</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.39045260355924</v>
+        <v>7.700948548078377</v>
       </c>
       <c r="D5" t="n">
-        <v>54.53639202913551</v>
+        <v>8.86216370473452</v>
       </c>
       <c r="E5" t="n">
-        <v>7.725566464509935</v>
+        <v>1.255404550482864</v>
       </c>
       <c r="F5" t="n">
-        <v>16.36849919180995</v>
+        <v>2.659881118669115</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.4386494384289</v>
+        <v>3.646280533744696</v>
       </c>
       <c r="D6" t="n">
-        <v>21.23525066652192</v>
+        <v>3.450728233309813</v>
       </c>
       <c r="E6" t="n">
-        <v>7.725566464509935</v>
+        <v>1.255404550482864</v>
       </c>
       <c r="F6" t="n">
-        <v>16.36849919180995</v>
+        <v>2.659881118669115</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>30.00762848769148</v>
+        <v>4.876239629249866</v>
       </c>
       <c r="D7" t="n">
-        <v>29.26174977679906</v>
+        <v>4.755034338729848</v>
       </c>
       <c r="E7" t="n">
-        <v>7.725566464509935</v>
+        <v>1.255404550482864</v>
       </c>
       <c r="F7" t="n">
-        <v>16.36849919180995</v>
+        <v>2.659881118669115</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.4952203202655</v>
+        <v>5.117973302043144</v>
       </c>
       <c r="D8" t="n">
-        <v>11.05364495068877</v>
+        <v>1.796217304486925</v>
       </c>
       <c r="E8" t="n">
-        <v>7.725566464509935</v>
+        <v>1.255404550482864</v>
       </c>
       <c r="F8" t="n">
-        <v>16.36849919180995</v>
+        <v>2.659881118669115</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
